--- a/templates/Capitânia Fapes - template.xlsx
+++ b/templates/Capitânia Fapes - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$H$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$H$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1318,14 +1318,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.28515625" defaultRowHeight="12.75"/>
   <cols>
     <col width="17.28515625" customWidth="1" style="60" min="1" max="1"/>
     <col width="18.7109375" customWidth="1" style="60" min="2" max="8"/>
     <col width="21.5703125" customWidth="1" style="60" min="9" max="9"/>
-    <col width="17.28515625" customWidth="1" style="60" min="10" max="17"/>
-    <col width="17.28515625" customWidth="1" style="60" min="18" max="16384"/>
+    <col width="17.28515625" customWidth="1" style="60" min="10" max="18"/>
+    <col width="17.28515625" customWidth="1" style="60" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1498,52 +1498,52 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="9">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
-        <v>188.906392</v>
+        <v>192.1849026</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>-0.002181276242688601</v>
+        <v>0.000964558760609302</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>-0.002775113762013337</v>
+        <v>0.003784363932781476</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>0.0005938375193247358</v>
+        <v>-0.002819805172172174</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>-0.0004173049558622299</v>
+        <v>0.001228260330804476</v>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-0.001763971286826371</v>
+        <v>-0.0002637015701951739</v>
       </c>
     </row>
     <row r="18" ht="15.95" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>189.3193498</v>
+        <v>191.9997076</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>-0.0006322928082184154</v>
+        <v>0.0005860008586344723</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.001280962415003195</v>
+        <v>0.001906502045387226</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>-0.00191325522322161</v>
+        <v>-0.001320501186752754</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>0.001008317718015572</v>
+        <v>0.001228864396657148</v>
       </c>
       <c r="H18" s="30" t="n">
-        <v>-0.001640610526233988</v>
+        <v>-0.0006428635380226755</v>
       </c>
       <c r="I18" s="4" t="n"/>
     </row>
@@ -1551,26 +1551,26 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>189.4391308</v>
+        <v>191.8872615</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>-0.001444719086885815</v>
+        <v>0.004784932259050079</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>-0.002016246470113892</v>
+        <v>0.005962594715911873</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>0.0005715273832280765</v>
+        <v>-0.001177662456861794</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>-0.000369098634551146</v>
+        <v>0.003055672154189226</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>-0.001075620452334669</v>
+        <v>0.001729260104860852</v>
       </c>
       <c r="I19" s="4" t="n"/>
     </row>
@@ -1578,26 +1578,26 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>189.7132131</v>
+        <v>190.9734664</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>-0.002068587725304272</v>
+        <v>-0.003606739869022491</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.002323937513367902</v>
+        <v>-8.847376162690601e-05</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>-0.004392525238672174</v>
+        <v>-0.003518266107395585</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>0.002424076115274953</v>
+        <v>0.0001401648621799367</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>-0.004492663840579225</v>
+        <v>-0.003746904731202427</v>
       </c>
       <c r="I20" s="4" t="n"/>
     </row>
@@ -1605,26 +1605,26 @@
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>190.106465</v>
+        <v>191.6647513</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>-0.003009041894913911</v>
+        <v>0.004631245716470556</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>-0.003517165775007047</v>
+        <v>0.001373673909628392</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>0.0005081238800931365</v>
+        <v>0.003257571806842163</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>-0.001141971242602069</v>
+        <v>-7.902904525247667e-05</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>-0.001867070652311842</v>
+        <v>0.004710274761723032</v>
       </c>
       <c r="I21" s="4" t="n"/>
     </row>
@@ -1678,24 +1678,24 @@
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="46" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="41" t="inlineStr"/>
       <c r="D24" s="41" t="n">
-        <v>-0.01176404818439036</v>
+        <v>0.009473643251726394</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>-0.008025264155480549</v>
+        <v>0.0157814657880031</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>-0.003738784028909814</v>
+        <v>-0.006307822536276708</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>0.006369420073854881</v>
+        <v>0.007488477748118338</v>
       </c>
       <c r="H24" s="27" t="n">
-        <v>-0.01813346825824524</v>
+        <v>0.001985165503608055</v>
       </c>
       <c r="I24" s="14" t="n"/>
     </row>
@@ -1708,19 +1708,19 @@
       </c>
       <c r="C25" s="42" t="inlineStr"/>
       <c r="D25" s="42" t="n">
-        <v>-0.009228556407117394</v>
+        <v>0.009399131249904435</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>-0.004366530544361868</v>
+        <v>0.02260048556561456</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>-0.004862025862755526</v>
+        <v>-0.01320135431571012</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>0.008564754015659926</v>
+        <v>0.02051942488737701</v>
       </c>
       <c r="H25" s="30" t="n">
-        <v>-0.01779331042277732</v>
+        <v>-0.01112029363747258</v>
       </c>
       <c r="I25" s="39" t="n"/>
     </row>
@@ -1733,19 +1733,19 @@
       </c>
       <c r="C26" s="42" t="inlineStr"/>
       <c r="D26" s="42" t="n">
-        <v>0.02315387108542533</v>
+        <v>0.0355684248660848</v>
       </c>
       <c r="E26" s="30" t="n">
-        <v>0.02705013376004373</v>
+        <v>0.04800146190063681</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>-0.0038962626746184</v>
+        <v>-0.01243303703455201</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>0.03540704738942546</v>
+        <v>0.04413395526982056</v>
       </c>
       <c r="H26" s="30" t="n">
-        <v>-0.01225317630400014</v>
+        <v>-0.008565530403735755</v>
       </c>
       <c r="I26" s="15" t="n"/>
     </row>
@@ -1758,19 +1758,19 @@
       </c>
       <c r="C27" s="42" t="inlineStr"/>
       <c r="D27" s="42" t="n">
-        <v>0.05376726915989005</v>
+        <v>0.06927116979086367</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>0.05228677744302912</v>
+        <v>0.08424100868653972</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>0.001480491716860932</v>
+        <v>-0.01496983889567605</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>0.06212331211768896</v>
+        <v>0.07820231730317562</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>-0.008356042957798904</v>
+        <v>-0.008931147512311943</v>
       </c>
       <c r="I27" s="15" t="n"/>
     </row>
@@ -1783,19 +1783,19 @@
       </c>
       <c r="C28" s="42" t="inlineStr"/>
       <c r="D28" s="42" t="n">
-        <v>0.1407571358472322</v>
+        <v>0.1497178929103125</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>0.1198792525684791</v>
+        <v>0.1412381166231067</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>0.02087788327875306</v>
+        <v>0.008479776287205754</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>0.1176647437940919</v>
+        <v>0.1297857302122285</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>0.02309239205314029</v>
+        <v>0.01993216269808396</v>
       </c>
       <c r="I28" s="15" t="n"/>
     </row>
@@ -1803,24 +1803,24 @@
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="47" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="42" t="inlineStr"/>
       <c r="D29" s="42" t="n">
-        <v>0.01862753666563943</v>
+        <v>0.2347263505283499</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>0.01985296752187793</v>
+        <v>0.1602720665516928</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>-0.001225430856238496</v>
+        <v>0.0744542839766571</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>0.03089355229913116</v>
+        <v>0.2160979564480416</v>
       </c>
       <c r="H29" s="30" t="n">
-        <v>-0.01226601563349172</v>
+        <v>0.01862839408030825</v>
       </c>
       <c r="I29" s="15" t="n"/>
     </row>
@@ -1828,130 +1828,138 @@
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="42" t="inlineStr"/>
       <c r="D30" s="42" t="n">
-        <v>0.1561369385750904</v>
+        <v>0.03630603415348599</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>0.1316812131695793</v>
+        <v>0.04606202995521769</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>0.02445572540551111</v>
+        <v>-0.009755995801731698</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>0.1165027532037295</v>
+        <v>0.04642807189443898</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>0.03963418537136087</v>
+        <v>-0.01012203774095299</v>
       </c>
       <c r="I30" s="15" t="n"/>
     </row>
-    <row r="31" ht="15.95" customFormat="1" customHeight="1" s="29">
-      <c r="A31" s="53" t="n"/>
+    <row r="31" ht="15.95" customHeight="1">
+      <c r="A31" s="10" t="n"/>
       <c r="B31" s="47" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="42" t="inlineStr"/>
       <c r="D31" s="42" t="n">
-        <v>0.06726229252583993</v>
+        <v>0.1561369385750904</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>-0.02439397265320542</v>
+        <v>0.1316812131695793</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>0.09165626517904535</v>
+        <v>0.02445572540551111</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>0.06161563642436141</v>
+        <v>0.1165027532037295</v>
       </c>
       <c r="H31" s="30" t="n">
-        <v>0.00564665610147852</v>
-      </c>
-    </row>
-    <row r="32" ht="15.95" customHeight="1">
+        <v>0.03963418537136087</v>
+      </c>
+      <c r="I31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="A32" s="53" t="n"/>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="42" t="inlineStr"/>
       <c r="D32" s="42" t="n">
-        <v>0.8890639200000001</v>
+        <v>0.06726229252583993</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>0.5297655856396559</v>
+        <v>-0.02439397265320542</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>0.3592983343603442</v>
+        <v>0.09165626517904535</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>0.677956628592147</v>
+        <v>0.06161563642436141</v>
       </c>
       <c r="H32" s="30" t="n">
-        <v>0.2111072914078531</v>
-      </c>
-      <c r="I32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="48">
-      <c r="A33" s="23" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="41" t="n"/>
-      <c r="D33" s="41" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="43" t="inlineStr">
+        <v>0.00564665610147852</v>
+      </c>
+    </row>
+    <row r="33" ht="15.95" customHeight="1">
+      <c r="A33" s="53" t="n"/>
+      <c r="B33" s="47" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr"/>
+      <c r="D33" s="42" t="n">
+        <v>0.9218490259999998</v>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>0.5690788229583914</v>
+      </c>
+      <c r="F33" s="30" t="n">
+        <v>0.3527702030416084</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>0.7032417320529336</v>
+      </c>
+      <c r="H33" s="30" t="n">
+        <v>0.2186072939470662</v>
+      </c>
+      <c r="I33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customFormat="1" customHeight="1" s="48">
+      <c r="A34" s="23" t="n"/>
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="41" t="n"/>
+      <c r="D34" s="41" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
+      <c r="H34" s="27" t="n"/>
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C34" s="43" t="n"/>
-      <c r="D34" s="43" t="n"/>
-      <c r="E34" s="43" t="n"/>
-      <c r="F34" s="43" t="n"/>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="43" t="n"/>
-      <c r="I34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="44" t="n">
-        <v>304278220.66</v>
-      </c>
-      <c r="F35" s="44" t="n"/>
-      <c r="G35" s="44" t="n"/>
-      <c r="H35" s="44" t="n"/>
+      <c r="C35" s="43" t="n"/>
+      <c r="D35" s="43" t="n"/>
+      <c r="E35" s="43" t="n"/>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="43" t="n"/>
       <c r="I35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="10" t="n"/>
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="32" t="n"/>
       <c r="D36" s="32" t="n"/>
       <c r="E36" s="44" t="n">
-        <v>287967670.9104762</v>
+        <v>309559033.91</v>
       </c>
       <c r="F36" s="44" t="n"/>
       <c r="G36" s="44" t="n"/>
@@ -1960,98 +1968,104 @@
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="10" t="n"/>
-      <c r="B37" s="31" t="n"/>
+      <c r="B37" s="33" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
       <c r="C37" s="32" t="n"/>
       <c r="D37" s="32" t="n"/>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="32" t="n"/>
-      <c r="H37" s="32" t="n"/>
+      <c r="E37" s="44" t="n">
+        <v>289522178.4037302</v>
+      </c>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="44" t="n"/>
+      <c r="H37" s="44" t="n"/>
       <c r="I37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
       <c r="A38" s="10" t="n"/>
-      <c r="B38" s="34" t="inlineStr">
-        <is>
-          <t>¹ Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="36" t="n"/>
+      <c r="B38" s="31" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="32" t="n"/>
+      <c r="F38" s="32" t="n"/>
+      <c r="G38" s="32" t="n"/>
+      <c r="H38" s="32" t="n"/>
       <c r="I38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="10" t="n"/>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">²Cota Inicial em: </t>
-        </is>
-      </c>
-      <c r="C39" s="37" t="inlineStr">
-        <is>
-          <t>2020-05-22</t>
-        </is>
-      </c>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="38" t="n"/>
-      <c r="H39" s="38" t="n"/>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>¹ Data de Referência:</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="36" t="n"/>
       <c r="I39" s="4" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="10" t="n"/>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="17" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="18" t="n"/>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">²Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="38" t="n"/>
+      <c r="H40" s="38" t="n"/>
       <c r="I40" s="4" t="n"/>
     </row>
-    <row r="41" ht="47.25" customHeight="1">
+    <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="10" t="n"/>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="47.25" customHeight="1">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="I41" s="4" t="n"/>
-    </row>
-    <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="59" t="n"/>
       <c r="I42" s="4" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="19" t="n"/>
+      <c r="B43" s="59" t="n"/>
       <c r="I43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="20" t="n"/>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="15" t="n"/>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="15" t="n"/>
-      <c r="H44" s="15" t="n"/>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="19" t="n"/>
       <c r="I44" s="4" t="n"/>
     </row>
     <row r="45">
@@ -2065,13 +2079,24 @@
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="4" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="4" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B41:H41"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="87" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="84"/>
 </worksheet>
 </file>